--- a/bookings_report.xlsx
+++ b/bookings_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
   <si>
     <t>ID Бронирования</t>
   </si>
@@ -27,6 +27,39 @@
   </si>
   <si>
     <t>Статус</t>
+  </si>
+  <si>
+    <t>2026-06-01T10:00</t>
+  </si>
+  <si>
+    <t>2026-06-02T12:00</t>
+  </si>
+  <si>
+    <t>2026-06-01T11:30</t>
+  </si>
+  <si>
+    <t>2026-06-03T14:00</t>
+  </si>
+  <si>
+    <t>2026-06-04T15:00</t>
+  </si>
+  <si>
+    <t>2026-06-05T09:00</t>
+  </si>
+  <si>
+    <t>2026-06-06T16:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T10:30</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:00</t>
+  </si>
+  <si>
+    <t>2026-06-09T13:00</t>
+  </si>
+  <si>
+    <t>2026-09-22T15:20</t>
   </si>
 </sst>
 </file>
@@ -87,7 +120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.78125" customWidth="true" bestFit="true"/>
@@ -114,6 +147,193 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>346.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
